--- a/Ryzyko.xlsx
+++ b/Ryzyko.xlsx
@@ -161,14 +161,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -469,79 +469,79 @@
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50" style="2" customWidth="1"/>
+    <col min="1" max="1" width="50" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="63" style="2" customWidth="1"/>
+    <col min="5" max="5" width="63" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
@@ -553,12 +553,12 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
@@ -566,7 +566,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
@@ -574,7 +574,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="s">
@@ -582,7 +582,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
@@ -590,7 +590,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
@@ -598,7 +598,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="s">
@@ -606,7 +606,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
@@ -614,7 +614,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="s">
@@ -622,7 +622,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B21" t="s">
@@ -630,7 +630,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B22" t="s">

--- a/Ryzyko.xlsx
+++ b/Ryzyko.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owcza\Desktop\nw\inzynieria-oprogramowania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6429108-176F-4246-BDDA-630D635DBD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39264F62-3CFB-4753-B417-FC658910245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="24">
   <si>
     <t>1. Poniżej wpiszcie numer indeksu i imię i nazwisko poszczególnych osób w zespole</t>
   </si>
@@ -564,6 +564,12 @@
       <c r="B13" t="s">
         <v>21</v>
       </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -572,6 +578,12 @@
       <c r="B14" t="s">
         <v>22</v>
       </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -580,6 +592,12 @@
       <c r="B15" t="s">
         <v>23</v>
       </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -588,53 +606,95 @@
       <c r="B16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Ryzyko.xlsx
+++ b/Ryzyko.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owcza\Desktop\nw\inzynieria-oprogramowania\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pawel\Desktop\Projects\inz-op\inzynieria-oprogramowania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39264F62-3CFB-4753-B417-FC658910245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EFD74E-9A32-4EB9-B19D-6BCD2CEB6137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ryzyko" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="25">
   <si>
     <t>1. Poniżej wpiszcie numer indeksu i imię i nazwisko poszczególnych osób w zespole</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Niskie</t>
+  </si>
+  <si>
+    <t>Stworzenie kopii zapasowej repozytorium</t>
   </si>
 </sst>
 </file>
@@ -613,7 +616,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -627,7 +630,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -640,8 +643,11 @@
       <c r="D18" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -655,7 +661,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -669,7 +675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -683,7 +689,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
